--- a/business_forms/034_financial_reporting_tool_request_form--business_forms.xlsx
+++ b/business_forms/034_financial_reporting_tool_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,12 +684,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'balance'}</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Balance'}</t>
+          <t>Balance</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cash_flow'}</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cash Flow'}</t>
+          <t>Cash Flow</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'income_statement'}</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Income Statement'}</t>
+          <t>Income Statement</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bi-annual'}</t>
+          <t>bi-annual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bi-Annual'}</t>
+          <t>Bi-Annual</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -836,29 +836,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chatjimmy'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'chatjimmy'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'chatjimmy'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'chatjimmy'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -870,29 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>reporting_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'weekly'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
